--- a/Podliczenie ZUS.xlsx
+++ b/Podliczenie ZUS.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84048ED6-A4A9-4B12-A95C-325CB00D3D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BDCB20-A04B-482D-8A37-D92B62E0CD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ZUS" sheetId="1" r:id="rId1"/>
@@ -685,20 +685,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="52">
@@ -1450,10 +1450,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="17"/>
+      <c r="C1" s="18"/>
     </row>
     <row r="2" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2"/>
@@ -1469,10 +1469,10 @@
       <c r="C4" s="5"/>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="16"/>
+      <c r="C5" s="17"/>
     </row>
     <row r="6" spans="2:3" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="10" t="s">
@@ -1576,12 +1576,12 @@
       <c r="C22" s="6"/>
     </row>
     <row r="23" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
     </row>
     <row r="24" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
     </row>
     <row r="25" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="15"/>
@@ -1596,20 +1596,8 @@
     <mergeCell ref="B1:C1"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
-  <dataValidations count="13">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Nazwa firmy jest automatycznie dodawana w tej komórce" sqref="B23" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="W tej kolumnie pod tym nagłówkiem wprowadź kwotę dla każdego opisu z kolumny B. Ostatnia komórka tabeli zawiera całkowitą kwotę należności" sqref="C8" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="W tej kolumnie pod tym nagłówkiem wprowadź opisy pozycji faktury" sqref="B8" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="W tej komórce wprowadź imię i nazwisko klienta" sqref="B6" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="W tej komórce wprowadź numer telefonu klienta" sqref="B7" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="W komórkach poniżej wprowadź imię i nazwisko klienta, nazwę jego firmy, ulicę i numer telefonu" sqref="B5 B1" xr:uid="{00000000-0002-0000-0000-00000A000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="W tej komórce w nawiasach kwadratowych wprowadź numer telefonu i faksu" sqref="B4" xr:uid="{00000000-0002-0000-0000-00000B000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="W tej komórce wprowadź motto firmy, a w poniższych komórkach adres firmy" sqref="B2" xr:uid="{00000000-0002-0000-0000-00000E000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="W tej komórce wprowadź opis produktu, którego dotyczy faktura" sqref="C4" xr:uid="{00000000-0002-0000-0000-00000F000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="W komórce z prawej strony wprowadź datę faktury" sqref="B3" xr:uid="{00000000-0002-0000-0000-000013000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="W tej komórce wprowadź datę faktury" sqref="C3" xr:uid="{00000000-0002-0000-0000-000014000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="W tym arkuszu utwórz fakturę z obliczeniem sumy. Wprowadź szczegóły dotyczące firmy i klienta oraz opisy i kwoty w tabeli faktury. Całkowita należność jest obliczana automatycznie" sqref="A1" xr:uid="{00000000-0002-0000-0000-000016000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="W tej komórce wprowadź imię i nazwisko, numer telefonu i adres e-mail osoby do kontaktu w firmie wystawiającej fakturę" sqref="B24:C24" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A1:C20 D1:F21 A22:F46" xr:uid="{B9022A08-48C6-495E-84C8-F45AB09A2F70}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1644,6 +1632,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac37c1753acd5e330d2062ccec26ea66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b340c7101c92c5120abd06486f94548" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1943,15 +1940,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54BA574B-D25A-47D2-A157-4CAA56EBF4AE}">
   <ds:schemaRefs>
@@ -1965,6 +1953,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E84B1AD-03C0-4B52-BD7A-D11E11AAE50D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FFA2500-0DAB-4D00-A350-6145D1830994}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1983,12 +1979,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E84B1AD-03C0-4B52-BD7A-D11E11AAE50D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>